--- a/templates/deliverable/example/06_DB표준도메인.xlsx
+++ b/templates/deliverable/example/06_DB표준도메인.xlsx
@@ -26,7 +26,7 @@
     <t>DB명</t>
   </si>
   <si>
-    <t>표준도메인그룹명</t>
+    <t>표준도메인 그룹명</t>
   </si>
   <si>
     <t>도메인분류명</t>
@@ -35,7 +35,7 @@
     <t>도메인명</t>
   </si>
   <si>
-    <t>도메인설명</t>
+    <t>도메인 설명</t>
   </si>
   <si>
     <t>데이터타입</t>
@@ -44,7 +44,7 @@
     <t>데이터길이</t>
   </si>
   <si>
-    <t>소수점길이</t>
+    <t>소수점 길이</t>
   </si>
   <si>
     <t>저장형식</t>
@@ -83,12 +83,12 @@
     </font>
     <font>
       <name val="Calibri"/>
-      <sz val="11.0"/>
+      <sz val="14.0"/>
       <b val="true"/>
     </font>
     <font>
       <name val="Calibri"/>
-      <sz val="14.0"/>
+      <sz val="11.0"/>
       <b val="true"/>
     </font>
   </fonts>
@@ -142,8 +142,8 @@
   </cellStyleXfs>
   <cellXfs count="4">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="true"/>
-    <xf numFmtId="0" fontId="1" fillId="3" borderId="4" xfId="0" applyBorder="true" applyFont="true" applyFill="true"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="true"/>
+    <xf numFmtId="0" fontId="2" fillId="3" borderId="4" xfId="0" applyBorder="true" applyFont="true" applyFill="true"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="4" xfId="0" applyBorder="true"/>
   </cellXfs>
 </styleSheet>
@@ -157,13 +157,13 @@
     <col min="1" max="1" width="8.0" customWidth="true"/>
     <col min="2" max="2" width="10.0" customWidth="true"/>
     <col min="3" max="3" width="10.0" customWidth="true"/>
-    <col min="4" max="4" width="20.0" customWidth="true"/>
+    <col min="4" max="4" width="22.0" customWidth="true"/>
     <col min="5" max="5" width="16.0" customWidth="true"/>
     <col min="6" max="6" width="12.0" customWidth="true"/>
-    <col min="7" max="7" width="14.0" customWidth="true"/>
+    <col min="7" max="7" width="16.0" customWidth="true"/>
     <col min="8" max="8" width="14.0" customWidth="true"/>
     <col min="9" max="9" width="14.0" customWidth="true"/>
-    <col min="10" max="10" width="14.0" customWidth="true"/>
+    <col min="10" max="10" width="16.0" customWidth="true"/>
     <col min="11" max="11" width="12.0" customWidth="true"/>
     <col min="12" max="12" width="12.0" customWidth="true"/>
     <col min="13" max="13" width="8.0" customWidth="true"/>
